--- a/inputs/tested/7268/header_map.xlsx
+++ b/inputs/tested/7268/header_map.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HeaderMap" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="valid_fields" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="notes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,14 +28,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="00666666"/>
-      <sz val="9"/>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -62,10 +63,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -431,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -441,211 +447,507 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Sixth client layout ('Append1' sheet, PDF-scraped). 'toevoeging' is intentionally NOT mapped -- it is a mixed qualifier column (position/brand/size/torque/protocol/assumption-flag) with no engine consumer, and its content is cosmetic only. Two rows ('Spanning aanwezig') carry '230V'/'24V' there describing a monitored rail on a status DI -- if it is ever mapped in future, it must NEVER feed voltage/current/power. Real electrical specs for powered devices are free text in 'Opmerking' ('230vac/6A', '400V/10A/4kW', 'EC,400V/2,2kW'), parsed by ingest.py's _parse_electrical_spec() fallback.</t>
+          <t>client_header</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>canonical_field</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>kast</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>rk</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>client_header</t>
+          <t>aantal</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>aantal</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>omschrijving</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>omschrijving</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Artikel</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Opmerking</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>opmerking</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>"B" melding</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>DI_bedrijf</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>"ST" melding</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>DI_storing</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>"Open" / Status / WS</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>DI_status</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>An.Ingang</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>An.Uitgang + Int.</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>AO</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Dig.Uitgang + Int.</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
           <t>canonical_field</t>
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>rk</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>procescode</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>omschrijving</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>fabricaat</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>aantal</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>AO</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>SOFT</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>power_kw</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>current_a</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>va</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>bus_protocol</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>bus_naam</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>derden_flag</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>locatie</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>regelkast_spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>opmerking</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>source_ref</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>DI_bedrijf</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>DI_storing</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>DI_status</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>mr_flag</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="112" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>onderwerp</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>toelichting</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>KOPREGEL</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Rij 1, sheet Append1. Geen merges, geen preamble - de eenvoudigste layout tot nu toe. De Page001-004 sheets hebben DEZELFDE kolomnamen maar op ANDERE posities (Page001/004 hebben een extra 'Column6'), dus deze map werkt op alle sheets omdat hij op naam matcht, niet op index.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>DUPLICAATPAAR: An.Uitgang</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>'An.Uitgang' en 'An.Uitgang + Int.' zouden allebei AO zijn. cols.setdefault houdt de EERSTE, dus alleen 'An.Uitgang + Int.' is gemapt. VEILIG: 'An.Uitgang' heeft 4 gevulde cellen met som 0 - hij is over de hele sheet leeg. 'An.Uitgang + Int.' heeft 25 cellen / 80 punten. Dit was de reden dat AO=0 was en de Energy Valves geen I/O-signatuur hadden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>DUPLICAATPAAR: Dig.Uitgang</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>HIER GAAT DATA VERLOREN. 'Dig.Uitgang' 8 cellen / 18 punten, 'Dig.Uitgang + Int.' 32 cellen / 122 punten. Beide bevatten data maar NORM_COLUMNS heeft maar een DO-veld (anders dan DI, dat DI_bedrijf + DI_storing + DI_status optelt). De grootste is gemapt; de 18 punten uit 'Dig.Uitgang' vallen weg. ECHTE OPLOSSING: een tweede DO-veld in het schema, of ingest laten optellen bij dubbele kolommen (zie Q23, vierde silent-drop mechanisme, 7222).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Wat betekent '+ Int.'</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Onbekend - waarschijnlijk 'inclusief interne punten'. De An.Uitgang-kolom is volledig leeg terwijl An.Uitgang + Int. gevuld is, dus de klant gebruikt in de praktijk alleen de +Int.-variant. VRAAG AAN RICK voordat de Dig.Uitgang-keuze definitief wordt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>"Open" / Status / WS</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Gemapt op DI_status, dat door ingest bij DI wordt opgeteld (samen met DI_bedrijf en DI_storing). 11 cellen / 40 punten. Als dit GEEN digitale ingang is, moet deze regel weg.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>BACnet / MODbus / M-bus punten</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>BEWUST NIET GEMAPT. Drie aparte telkolommen: BACnet 10 cellen/76, MODbus 9/286, M-bus 6/52. Het PROTOCOL blijkt uit WELKE kolom gevuld is, niet uit een naam - een header map kan dat niet uitdrukken. Gevolg: bus_protocol blijft leeg en _bus_row emit GEEN buskabel. Dat is de reden dat de Energy Valves hun BACnet-kabel (COMM U/UTP CAT6 CS34ZB HA305) missen en dat Water-meter / Bedrijfs Water-meter NO CABLE DERIVED geven. Derde variant na 7222 (kolom 'Busprotocol' met protocolnaam) en 7-nieuw (kolommen 'Sturen'/'Meten'). Vraagt om een regel in ingest of een pre-pass, niet om een mapregel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>toevoeging</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>NIET GEMAPT. Gemengde inhoud: 'Belimo' (fabrikant), maar ook 'aanvoer', 'DN40-65', '7 Nm', '(aanname)', '230V', 'MODbus'. Mappen op fabricaat zou onzin in die kolom zetten. 46 cellen. Overweeg opmerking, maar dat botst met de bestaande 'Opmerking'-kolom (setdefault).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>omschrijving bevat groepskoppen</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Sommige cellen hebben een newline met de groepskop erin, bv. 'condensorzijdig\nDompeltemperatuur opnemer'. De groepsstructuur zit dus IN de devicenaam. Ongemapt laten kan niet - omschrijving is verplicht - maar de groep gaat zo verloren en de naam bevat ruis die classify_row meeleest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>kast</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>rk</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>aantal</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>aantal</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>omschrijving</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>omschrijving</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>dig.uitgang</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>DO</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>dig.uitgang + int.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>DO</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>"b" melding</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>DI</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>"st" melding</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>DI</t>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Waarden bevatten newlines ('RK1\nRK1'). Gemapt op rk; als run_per_rk hierop groepeert kunnen 'RK1' en 'RK1\nRK1' als twee panelen tellen. Controleren in de output.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>"open" / status / ws</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>DI</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>an.ingang</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>an.uitgang</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>AO</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>an.uitgang + int.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>AO</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>bacnet-punten</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>SOFT</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>modbus-punten</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>SOFT</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>m-bus-punten</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>SOFT</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>artikel</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>opmerking</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>opmerking</t>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>procescode</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Deze layout heeft GEEN procescode-kolom. _prefix geeft overal 0, dus groepsvolgorde is inert en de rijvolgorde valt terug op invoervolgorde. Vierde project op rij.</t>
         </is>
       </c>
     </row>
